--- a/process_1_results.xlsx
+++ b/process_1_results.xlsx
@@ -43,37 +43,37 @@
     <t>Token-2</t>
   </si>
   <si>
+    <t>Token-5</t>
+  </si>
+  <si>
     <t>Token-3</t>
   </si>
   <si>
-    <t>Token-5</t>
-  </si>
-  <si>
     <t>Token-4</t>
   </si>
   <si>
     <t>Token-6</t>
   </si>
   <si>
+    <t>Token-8</t>
+  </si>
+  <si>
+    <t>Token-9</t>
+  </si>
+  <si>
+    <t>Token-10</t>
+  </si>
+  <si>
     <t>Token-7</t>
   </si>
   <si>
-    <t>Token-8</t>
-  </si>
-  <si>
-    <t>Token-9</t>
-  </si>
-  <si>
-    <t>Token-10</t>
-  </si>
-  <si>
     <t>Start -&gt; Start -&gt; Step 1 -&gt; Step 2 -&gt; Step 3 -&gt; Stop</t>
   </si>
   <si>
+    <t>Start -&gt; Start -&gt; Step 1 -&gt; Step 1 -&gt; Step 2 -&gt; Step 3 -&gt; Step 3 -&gt; Stop</t>
+  </si>
+  <si>
     <t>Start -&gt; Start -&gt; Step 1 -&gt; Step 2 -&gt; Step 3 -&gt; Step 3 -&gt; Stop</t>
-  </si>
-  <si>
-    <t>Start -&gt; Start -&gt; Step 1 -&gt; Step 1 -&gt; Step 2 -&gt; Step 3 -&gt; Step 3 -&gt; Stop</t>
   </si>
   <si>
     <t>Activity</t>
@@ -541,10 +541,10 @@
         <v>45754.29166666666</v>
       </c>
       <c r="C2" s="2">
-        <v>45754.3068678145</v>
+        <v>45754.30374175416</v>
       </c>
       <c r="D2">
-        <v>21.89</v>
+        <v>17.39</v>
       </c>
       <c r="E2">
         <v>0</v>
@@ -561,13 +561,13 @@
         <v>45754.29333082219</v>
       </c>
       <c r="C3" s="2">
-        <v>45754.30809197479</v>
+        <v>45754.30405346528</v>
       </c>
       <c r="D3">
-        <v>21.26</v>
+        <v>15.44</v>
       </c>
       <c r="E3">
-        <v>2.72</v>
+        <v>2.97</v>
       </c>
       <c r="F3" t="s">
         <v>17</v>
@@ -578,19 +578,19 @@
         <v>8</v>
       </c>
       <c r="B4" s="2">
-        <v>45754.29482309613</v>
+        <v>45754.29773647347</v>
       </c>
       <c r="C4" s="2">
-        <v>45754.31067943794</v>
+        <v>45754.3094768753</v>
       </c>
       <c r="D4">
-        <v>22.83</v>
+        <v>16.91</v>
       </c>
       <c r="E4">
-        <v>4.24</v>
+        <v>0</v>
       </c>
       <c r="F4" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
     </row>
     <row r="5" spans="1:6">
@@ -598,16 +598,16 @@
         <v>9</v>
       </c>
       <c r="B5" s="2">
-        <v>45754.29773647347</v>
+        <v>45754.29482309613</v>
       </c>
       <c r="C5" s="2">
-        <v>45754.31408437117</v>
+        <v>45754.31088469193</v>
       </c>
       <c r="D5">
-        <v>23.54</v>
+        <v>23.13</v>
       </c>
       <c r="E5">
-        <v>3.36</v>
+        <v>4.3</v>
       </c>
       <c r="F5" t="s">
         <v>17</v>
@@ -621,13 +621,13 @@
         <v>45754.29649597544</v>
       </c>
       <c r="C6" s="2">
-        <v>45754.3197060587</v>
+        <v>45754.3125551354</v>
       </c>
       <c r="D6">
-        <v>33.42</v>
+        <v>23.13</v>
       </c>
       <c r="E6">
-        <v>3.93</v>
+        <v>5.03</v>
       </c>
       <c r="F6" t="s">
         <v>17</v>
@@ -641,13 +641,13 @@
         <v>45754.29977929655</v>
       </c>
       <c r="C7" s="2">
-        <v>45754.32019703015</v>
+        <v>45754.31526807234</v>
       </c>
       <c r="D7">
-        <v>29.4</v>
+        <v>22.3</v>
       </c>
       <c r="E7">
-        <v>5.39</v>
+        <v>8.1</v>
       </c>
       <c r="F7" t="s">
         <v>17</v>
@@ -658,19 +658,19 @@
         <v>12</v>
       </c>
       <c r="B8" s="2">
-        <v>45754.30184261729</v>
+        <v>45754.30361905415</v>
       </c>
       <c r="C8" s="2">
-        <v>45754.32228044036</v>
+        <v>45754.31702144028</v>
       </c>
       <c r="D8">
-        <v>29.43</v>
+        <v>19.3</v>
       </c>
       <c r="E8">
-        <v>7.23</v>
+        <v>10.39</v>
       </c>
       <c r="F8" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
     </row>
     <row r="9" spans="1:6">
@@ -678,16 +678,16 @@
         <v>13</v>
       </c>
       <c r="B9" s="2">
-        <v>45754.30361905415</v>
+        <v>45754.30479496883</v>
       </c>
       <c r="C9" s="2">
-        <v>45754.32530760337</v>
+        <v>45754.32087893973</v>
       </c>
       <c r="D9">
-        <v>31.23</v>
+        <v>23.16</v>
       </c>
       <c r="E9">
-        <v>11.57</v>
+        <v>8.619999999999999</v>
       </c>
       <c r="F9" t="s">
         <v>18</v>
@@ -698,19 +698,19 @@
         <v>14</v>
       </c>
       <c r="B10" s="2">
-        <v>45754.30479496883</v>
+        <v>45754.30639505731</v>
       </c>
       <c r="C10" s="2">
-        <v>45754.32746002516</v>
+        <v>45754.32571461939</v>
       </c>
       <c r="D10">
-        <v>32.64</v>
+        <v>27.82</v>
       </c>
       <c r="E10">
-        <v>13.6</v>
+        <v>14.26</v>
       </c>
       <c r="F10" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
     </row>
     <row r="11" spans="1:6">
@@ -718,19 +718,19 @@
         <v>15</v>
       </c>
       <c r="B11" s="2">
-        <v>45754.30639505731</v>
+        <v>45754.30184261729</v>
       </c>
       <c r="C11" s="2">
-        <v>45754.33230253125</v>
+        <v>45754.32671378944</v>
       </c>
       <c r="D11">
-        <v>37.31</v>
+        <v>35.81</v>
       </c>
       <c r="E11">
-        <v>10.94</v>
+        <v>11.87</v>
       </c>
       <c r="F11" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
     </row>
   </sheetData>
@@ -774,13 +774,13 @@
         <v>10</v>
       </c>
       <c r="D2">
-        <v>6.48</v>
+        <v>3.64</v>
       </c>
       <c r="E2">
         <v>0</v>
       </c>
       <c r="F2">
-        <v>6.48</v>
+        <v>3.64</v>
       </c>
     </row>
     <row r="3" spans="1:6">
@@ -794,13 +794,13 @@
         <v>10</v>
       </c>
       <c r="D3">
-        <v>1.11</v>
+        <v>1.21</v>
       </c>
       <c r="E3">
-        <v>1.44</v>
+        <v>1.5</v>
       </c>
       <c r="F3">
-        <v>2.55</v>
+        <v>2.71</v>
       </c>
     </row>
     <row r="4" spans="1:6">
@@ -814,13 +814,13 @@
         <v>10</v>
       </c>
       <c r="D4">
-        <v>5.86</v>
+        <v>3.98</v>
       </c>
       <c r="E4">
         <v>0</v>
       </c>
       <c r="F4">
-        <v>5.86</v>
+        <v>3.98</v>
       </c>
     </row>
     <row r="5" spans="1:6">
@@ -834,13 +834,13 @@
         <v>10</v>
       </c>
       <c r="D5">
-        <v>3.95</v>
+        <v>3.33</v>
       </c>
       <c r="E5">
-        <v>6.68</v>
+        <v>7.25</v>
       </c>
       <c r="F5">
-        <v>10.62</v>
+        <v>10.58</v>
       </c>
     </row>
     <row r="6" spans="1:6">
@@ -854,13 +854,13 @@
         <v>10</v>
       </c>
       <c r="D6">
-        <v>4.6</v>
+        <v>3.73</v>
       </c>
       <c r="E6">
         <v>0</v>
       </c>
       <c r="F6">
-        <v>4.6</v>
+        <v>3.73</v>
       </c>
     </row>
   </sheetData>
@@ -886,7 +886,7 @@
         <v>32</v>
       </c>
       <c r="B2">
-        <v>0.3480737795138889</v>
+        <v>0.4028085121527777</v>
       </c>
     </row>
     <row r="3" spans="1:2">
@@ -894,7 +894,7 @@
         <v>33</v>
       </c>
       <c r="B3">
-        <v>1.370492759837963</v>
+        <v>1.154780180555556</v>
       </c>
     </row>
   </sheetData>
@@ -976,7 +976,7 @@
         <v>43</v>
       </c>
       <c r="B9">
-        <v>28.3</v>
+        <v>22.44</v>
       </c>
     </row>
   </sheetData>

--- a/process_1_results.xlsx
+++ b/process_1_results.xlsx
@@ -43,18 +43,21 @@
     <t>Token-2</t>
   </si>
   <si>
+    <t>Token-3</t>
+  </si>
+  <si>
     <t>Token-5</t>
   </si>
   <si>
-    <t>Token-3</t>
-  </si>
-  <si>
     <t>Token-4</t>
   </si>
   <si>
     <t>Token-6</t>
   </si>
   <si>
+    <t>Token-7</t>
+  </si>
+  <si>
     <t>Token-8</t>
   </si>
   <si>
@@ -64,16 +67,13 @@
     <t>Token-10</t>
   </si>
   <si>
-    <t>Token-7</t>
-  </si>
-  <si>
     <t>Start -&gt; Start -&gt; Step 1 -&gt; Step 2 -&gt; Step 3 -&gt; Stop</t>
   </si>
   <si>
+    <t>Start -&gt; Start -&gt; Step 1 -&gt; Step 2 -&gt; Step 3 -&gt; Step 3 -&gt; Stop</t>
+  </si>
+  <si>
     <t>Start -&gt; Start -&gt; Step 1 -&gt; Step 1 -&gt; Step 2 -&gt; Step 3 -&gt; Step 3 -&gt; Stop</t>
-  </si>
-  <si>
-    <t>Start -&gt; Start -&gt; Step 1 -&gt; Step 2 -&gt; Step 3 -&gt; Step 3 -&gt; Stop</t>
   </si>
   <si>
     <t>Activity</t>
@@ -541,10 +541,10 @@
         <v>45754.29166666666</v>
       </c>
       <c r="C2" s="2">
-        <v>45754.30374175416</v>
+        <v>45754.3068678145</v>
       </c>
       <c r="D2">
-        <v>17.39</v>
+        <v>21.89</v>
       </c>
       <c r="E2">
         <v>0</v>
@@ -561,13 +561,13 @@
         <v>45754.29333082219</v>
       </c>
       <c r="C3" s="2">
-        <v>45754.30405346528</v>
+        <v>45754.30809197479</v>
       </c>
       <c r="D3">
-        <v>15.44</v>
+        <v>21.26</v>
       </c>
       <c r="E3">
-        <v>2.97</v>
+        <v>2.72</v>
       </c>
       <c r="F3" t="s">
         <v>17</v>
@@ -578,19 +578,19 @@
         <v>8</v>
       </c>
       <c r="B4" s="2">
-        <v>45754.29773647347</v>
+        <v>45754.29482309613</v>
       </c>
       <c r="C4" s="2">
-        <v>45754.3094768753</v>
+        <v>45754.31067943794</v>
       </c>
       <c r="D4">
-        <v>16.91</v>
+        <v>22.83</v>
       </c>
       <c r="E4">
-        <v>0</v>
+        <v>4.24</v>
       </c>
       <c r="F4" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
     </row>
     <row r="5" spans="1:6">
@@ -598,16 +598,16 @@
         <v>9</v>
       </c>
       <c r="B5" s="2">
-        <v>45754.29482309613</v>
+        <v>45754.29773647347</v>
       </c>
       <c r="C5" s="2">
-        <v>45754.31088469193</v>
+        <v>45754.31408437117</v>
       </c>
       <c r="D5">
-        <v>23.13</v>
+        <v>23.54</v>
       </c>
       <c r="E5">
-        <v>4.3</v>
+        <v>3.36</v>
       </c>
       <c r="F5" t="s">
         <v>17</v>
@@ -621,13 +621,13 @@
         <v>45754.29649597544</v>
       </c>
       <c r="C6" s="2">
-        <v>45754.3125551354</v>
+        <v>45754.3197060587</v>
       </c>
       <c r="D6">
-        <v>23.13</v>
+        <v>33.42</v>
       </c>
       <c r="E6">
-        <v>5.03</v>
+        <v>3.93</v>
       </c>
       <c r="F6" t="s">
         <v>17</v>
@@ -641,13 +641,13 @@
         <v>45754.29977929655</v>
       </c>
       <c r="C7" s="2">
-        <v>45754.31526807234</v>
+        <v>45754.32019703015</v>
       </c>
       <c r="D7">
-        <v>22.3</v>
+        <v>29.4</v>
       </c>
       <c r="E7">
-        <v>8.1</v>
+        <v>5.39</v>
       </c>
       <c r="F7" t="s">
         <v>17</v>
@@ -658,19 +658,19 @@
         <v>12</v>
       </c>
       <c r="B8" s="2">
-        <v>45754.30361905415</v>
+        <v>45754.30184261729</v>
       </c>
       <c r="C8" s="2">
-        <v>45754.31702144028</v>
+        <v>45754.32228044036</v>
       </c>
       <c r="D8">
-        <v>19.3</v>
+        <v>29.43</v>
       </c>
       <c r="E8">
-        <v>10.39</v>
+        <v>7.23</v>
       </c>
       <c r="F8" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
     </row>
     <row r="9" spans="1:6">
@@ -678,16 +678,16 @@
         <v>13</v>
       </c>
       <c r="B9" s="2">
-        <v>45754.30479496883</v>
+        <v>45754.30361905415</v>
       </c>
       <c r="C9" s="2">
-        <v>45754.32087893973</v>
+        <v>45754.32530760337</v>
       </c>
       <c r="D9">
-        <v>23.16</v>
+        <v>31.23</v>
       </c>
       <c r="E9">
-        <v>8.619999999999999</v>
+        <v>11.57</v>
       </c>
       <c r="F9" t="s">
         <v>18</v>
@@ -698,19 +698,19 @@
         <v>14</v>
       </c>
       <c r="B10" s="2">
-        <v>45754.30639505731</v>
+        <v>45754.30479496883</v>
       </c>
       <c r="C10" s="2">
-        <v>45754.32571461939</v>
+        <v>45754.32746002516</v>
       </c>
       <c r="D10">
-        <v>27.82</v>
+        <v>32.64</v>
       </c>
       <c r="E10">
-        <v>14.26</v>
+        <v>13.6</v>
       </c>
       <c r="F10" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
     </row>
     <row r="11" spans="1:6">
@@ -718,19 +718,19 @@
         <v>15</v>
       </c>
       <c r="B11" s="2">
-        <v>45754.30184261729</v>
+        <v>45754.30639505731</v>
       </c>
       <c r="C11" s="2">
-        <v>45754.32671378944</v>
+        <v>45754.33230253125</v>
       </c>
       <c r="D11">
-        <v>35.81</v>
+        <v>37.31</v>
       </c>
       <c r="E11">
-        <v>11.87</v>
+        <v>10.94</v>
       </c>
       <c r="F11" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
     </row>
   </sheetData>
@@ -774,13 +774,13 @@
         <v>10</v>
       </c>
       <c r="D2">
-        <v>3.64</v>
+        <v>6.48</v>
       </c>
       <c r="E2">
         <v>0</v>
       </c>
       <c r="F2">
-        <v>3.64</v>
+        <v>6.48</v>
       </c>
     </row>
     <row r="3" spans="1:6">
@@ -794,13 +794,13 @@
         <v>10</v>
       </c>
       <c r="D3">
-        <v>1.21</v>
+        <v>1.11</v>
       </c>
       <c r="E3">
-        <v>1.5</v>
+        <v>1.44</v>
       </c>
       <c r="F3">
-        <v>2.71</v>
+        <v>2.55</v>
       </c>
     </row>
     <row r="4" spans="1:6">
@@ -814,13 +814,13 @@
         <v>10</v>
       </c>
       <c r="D4">
-        <v>3.98</v>
+        <v>5.86</v>
       </c>
       <c r="E4">
         <v>0</v>
       </c>
       <c r="F4">
-        <v>3.98</v>
+        <v>5.86</v>
       </c>
     </row>
     <row r="5" spans="1:6">
@@ -834,13 +834,13 @@
         <v>10</v>
       </c>
       <c r="D5">
-        <v>3.33</v>
+        <v>3.95</v>
       </c>
       <c r="E5">
-        <v>7.25</v>
+        <v>6.68</v>
       </c>
       <c r="F5">
-        <v>10.58</v>
+        <v>10.62</v>
       </c>
     </row>
     <row r="6" spans="1:6">
@@ -854,13 +854,13 @@
         <v>10</v>
       </c>
       <c r="D6">
-        <v>3.73</v>
+        <v>4.6</v>
       </c>
       <c r="E6">
         <v>0</v>
       </c>
       <c r="F6">
-        <v>3.73</v>
+        <v>4.6</v>
       </c>
     </row>
   </sheetData>
@@ -886,7 +886,7 @@
         <v>32</v>
       </c>
       <c r="B2">
-        <v>0.4028085121527777</v>
+        <v>0.3480737795138889</v>
       </c>
     </row>
     <row r="3" spans="1:2">
@@ -894,7 +894,7 @@
         <v>33</v>
       </c>
       <c r="B3">
-        <v>1.154780180555556</v>
+        <v>1.370492759837963</v>
       </c>
     </row>
   </sheetData>
@@ -976,7 +976,7 @@
         <v>43</v>
       </c>
       <c r="B9">
-        <v>22.44</v>
+        <v>28.3</v>
       </c>
     </row>
   </sheetData>
